--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>123536725</v>
       </c>
       <c r="B7" t="n">
-        <v>94996</v>
+        <v>95013</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>123536725</v>
       </c>
       <c r="B7" t="n">
-        <v>95013</v>
+        <v>95019</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>123536725</v>
       </c>
       <c r="B7" t="n">
-        <v>95019</v>
+        <v>95021</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>123536725</v>
       </c>
       <c r="B7" t="n">
-        <v>95021</v>
+        <v>95529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1359,6 +1359,122 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126135982</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58020</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogsväg S Svinasjön, Heby-Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>621585</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6657128</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ragnar Hall</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ragnar Hall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1364,7 +1364,7 @@
         <v>126135982</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1364,7 +1364,7 @@
         <v>126135982</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1364,7 +1364,7 @@
         <v>126135982</v>
       </c>
       <c r="B8" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1475,6 +1475,127 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131458190</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57728</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>vägobs, Heby-Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>621964</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6657071</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På relativt långt håll i öster</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bo Söderström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bo Söderström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>131458190</v>
       </c>
       <c r="B9" t="n">
-        <v>57728</v>
+        <v>57729</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>131458190</v>
       </c>
       <c r="B9" t="n">
-        <v>57729</v>
+        <v>57732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>131458190</v>
       </c>
       <c r="B9" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>132352981</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>132352981</v>
       </c>
       <c r="B9" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1480,7 +1480,7 @@
         <v>132352981</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1596,6 +1596,220 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134215145</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98043</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svinasjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>621525</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6657174</v>
+      </c>
+      <c r="S10" t="n">
+        <v>13</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134215147</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99095</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svinasjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>621516</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6657276</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1810,6 +1810,118 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134193599</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svinasjön NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>621411</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6657491</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1601,7 +1601,7 @@
         <v>134215145</v>
       </c>
       <c r="B10" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>134215147</v>
       </c>
       <c r="B11" t="n">
-        <v>99095</v>
+        <v>99097</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1922,6 +1922,228 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134348161</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>svinasjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>621432</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6657364</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Wåge Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Wåge Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134348162</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91980</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>svinasjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>621472</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6657319</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Wåge Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Wåge Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>134215145</v>
       </c>
       <c r="B10" t="n">
-        <v>98045</v>
+        <v>98046</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>134215147</v>
       </c>
       <c r="B11" t="n">
-        <v>99097</v>
+        <v>99098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>134348161</v>
       </c>
       <c r="B13" t="n">
-        <v>106309</v>
+        <v>106310</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>134348162</v>
       </c>
       <c r="B14" t="n">
-        <v>91980</v>
+        <v>91981</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1601,7 +1601,7 @@
         <v>134215145</v>
       </c>
       <c r="B10" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>134215147</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>99105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>134348161</v>
       </c>
       <c r="B13" t="n">
-        <v>106310</v>
+        <v>106317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>134348162</v>
       </c>
       <c r="B14" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,6 +2143,118 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134348160</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219788</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>svinasjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>621432</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6657364</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Wåge Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Wåge Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108911051</v>
+        <v>115432592</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Galtström, Upl</t>
+          <t>Galtström, Galtström, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621736.7419117305</v>
+        <v>621777</v>
       </c>
       <c r="R2" t="n">
-        <v>6657388.320193748</v>
+        <v>6657403</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,22 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Under granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +787,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115432896</v>
+        <v>123536725</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Galtström (Galtström), Upl</t>
+          <t>Galtström, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621784</v>
+        <v>621737</v>
       </c>
       <c r="R3" t="n">
-        <v>6657394</v>
+        <v>6657388</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,22 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,50 +903,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115432741</v>
+        <v>134348162</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Galtström (Galtström), Upl</t>
+          <t>svinasjö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621838</v>
+        <v>621472</v>
       </c>
       <c r="R4" t="n">
-        <v>6657388</v>
+        <v>6657319</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,27 +972,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Några enstaka Bladrosetter</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,62 +1002,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Wåge Gustafsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Wåge Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115433059</v>
+        <v>108911051</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Galtström (Galtström), Upl</t>
+          <t>Galtström, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621618</v>
+        <v>621737</v>
       </c>
       <c r="R5" t="n">
-        <v>6657241</v>
+        <v>6657388</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,22 +1079,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:22</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:22</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,53 +1111,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115432699</v>
+        <v>132352981</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Galtström (Galtström), Upl</t>
+          <t>Skogsväg S Svinasjön, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621798</v>
+        <v>621585</v>
       </c>
       <c r="R6" t="n">
-        <v>6657363</v>
+        <v>6657128</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1185,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Det drillande flyktlätet.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,27 +1220,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Ragnar Hall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Ragnar Hall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123536725</v>
+        <v>134193599</v>
       </c>
       <c r="B7" t="n">
-        <v>95551</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,46 +1243,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Galtström, Upl</t>
+          <t>Svinasjön NR, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621737</v>
+        <v>621411</v>
       </c>
       <c r="R7" t="n">
-        <v>6657388</v>
+        <v>6657491</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,22 +1302,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1332,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126135982</v>
+        <v>134193689</v>
       </c>
       <c r="B8" t="n">
-        <v>58027</v>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,46 +1355,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skogsväg S Svinasjön, Heby-Råksjön, Upl</t>
+          <t>Svinasjön NR, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621585</v>
+        <v>621393</v>
       </c>
       <c r="R8" t="n">
-        <v>6657128</v>
+        <v>6657515</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,22 +1419,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Knappt 50 vinterkrok från tupp. På hällmark, ej under mattall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,69 +1454,70 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ragnar Hall</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ragnar Hall</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132352981</v>
+        <v>134194478</v>
       </c>
       <c r="B9" t="n">
-        <v>57954</v>
+        <v>57162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skogsväg S Svinasjön, Heby-Råksjön, Upl</t>
+          <t>Svinasjön NR, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621585</v>
+        <v>621408</v>
       </c>
       <c r="R9" t="n">
-        <v>6657128</v>
+        <v>6657537</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,27 +1541,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Det drillande flyktlätet.</t>
+          <t>Tio tuppkrok från vintern.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1576,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ragnar Hall</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ragnar Hall</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134215145</v>
+        <v>134215143</v>
       </c>
       <c r="B10" t="n">
-        <v>98053</v>
+        <v>57162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,21 +1599,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1633,13 +1623,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621525</v>
+        <v>621672</v>
       </c>
       <c r="R10" t="n">
-        <v>6657174</v>
+        <v>6657133</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1668,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,48 +1700,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134215147</v>
+        <v>64828530</v>
       </c>
       <c r="B11" t="n">
-        <v>99105</v>
+        <v>5482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>101920</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svinasjön, Upl</t>
+          <t>Djupdalsåsen, N om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621516</v>
+        <v>622165</v>
       </c>
       <c r="R11" t="n">
-        <v>6657276</v>
+        <v>6657267</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1770,22 +1770,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:19</t>
+          <t>2017-04-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:19</t>
+          <t>2017-04-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,26 +1786,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>40 flyghål (över 10m stamved) på tallåga</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134193599</v>
+        <v>134215144</v>
       </c>
       <c r="B12" t="n">
-        <v>57162</v>
+        <v>57165</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1823,42 +1818,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svinasjön NR, Upl</t>
+          <t>Svinasjön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621411</v>
+        <v>621611</v>
       </c>
       <c r="R12" t="n">
-        <v>6657491</v>
+        <v>6657149</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,7 +1877,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,7 +1887,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,22 +1907,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134348161</v>
+        <v>126135982</v>
       </c>
       <c r="B13" t="n">
-        <v>106317</v>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,21 +1930,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1957,19 +1952,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>svinasjö, Upl</t>
+          <t>Skogsväg S Svinasjön, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621432</v>
+        <v>621585</v>
       </c>
       <c r="R13" t="n">
-        <v>6657364</v>
+        <v>6657128</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1993,22 +1993,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,44 +2023,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Wåge Gustafsson</t>
+          <t>Ragnar Hall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Wåge Gustafsson</t>
+          <t>Ragnar Hall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134348162</v>
+        <v>134348160</v>
       </c>
       <c r="B14" t="n">
-        <v>91988</v>
+        <v>99103</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>219788</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621472</v>
+        <v>621432</v>
       </c>
       <c r="R14" t="n">
-        <v>6657319</v>
+        <v>6657364</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,6 +2128,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2146,10 +2147,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134348160</v>
+        <v>134215147</v>
       </c>
       <c r="B15" t="n">
-        <v>99096</v>
+        <v>99112</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,16 +2158,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219788</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2174,24 +2175,20 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>svinasjö, Upl</t>
+          <t>Svinasjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621432</v>
+        <v>621516</v>
       </c>
       <c r="R15" t="n">
-        <v>6657364</v>
+        <v>6657276</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2220,7 +2217,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,7 +2227,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2239,22 +2236,672 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>115432699</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>621798</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6657363</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>115432741</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>621838</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6657388</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Några enstaka Bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>115432896</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>621784</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6657394</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>115433059</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>621618</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6657241</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134348161</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>svinasjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>621432</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6657364</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Wåge Gustafsson</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Wåge Gustafsson</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134215145</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Svinasjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>621525</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6657174</v>
+      </c>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Harbo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32759-2023 artfynd.xlsx
+++ b/artfynd/A 32759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134348162</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132352981</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134193599</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134193689</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1260,6 +1285,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134194478</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1376,6 +1406,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126135982</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1488,6 +1523,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134348160</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1595,6 +1635,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215147</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1706,6 +1751,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134348161</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1813,6 +1863,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215145</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1925,6 +1980,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115432592</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2041,6 +2101,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123536725</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2138,6 +2203,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108911051</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2250,6 +2320,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215143</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2357,6 +2432,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64828530</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2469,6 +2549,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134215144</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2576,6 +2661,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115432699</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2688,6 +2778,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115432741</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2795,6 +2890,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115432896</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2902,8 +3002,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115433059</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>